--- a/human_validation/judge/kor/judge_D019_S005_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S005_P001__qwen3-235b_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -559,12 +556,376 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 요즘 너무 이상하고 무서운 느낌이 들어서 왔어요. 캠퍼스를 걸어갈 때면 마치 유리 너머로 모든 걸 보는 것 같고, 제 몸 안에 완전히 있지 않은 것 같은 느낌이 들어요. 주변 건물이랑 학생들이 뭔가 진짜가 아닌 것처럼 느껴지는데, 그게 저를 무섭게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 요즘 거의 매일, 하루 대부분 기분이 가라앉거나 우울하다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 그런 것 같지는 않아요. 그러니까, 속상하고 무섭긴 했는데, 매일 하루 대부분 우울했다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이런 비현실감이나 자신과 동떨어진 느낌이 자주 일어나나요, 아니면 왔다 갔다 하나요? 이런 느낌을 겪으신 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 왔다 갔다 하는데, 그래도 꽤 자주 일어나서 정말 무서워요. 주로 캠퍼스를 걸어갈 때 갑자기 유리 너머로 모든 걸 보고 있는 것 같은 느낌이 들어요, 제 몸에 완전히 있지 않은 것처럼요. 주변 건물이랑 사람들이 한동안 그냥 비현실적으로 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이런 비현실감과 동떨어진 느낌이 특정한 일로 스트레스를 받거나 불안할 때 더 자주 일어나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 네, 이미 긴장했거나 걱정될 때 더 그런 것 같아요. 근데 정말 저를 무섭게 하는 부분은 캠퍼스를 걸어갈 때 갑자기 유리 너머로 모든 걸 보는 느낌이 드는 거예요, 제 몸에 완전히 있지 않은 것처럼요. 주변 건물이랑 학생들이 그냥... 뭔가 진짜가 아닌 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이런 비현실감이나 자신과 동떨어진 느낌이 오래 지속되나요, 아니면 늘 시간이 지나면 사라지나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 시간이 지나면 사라지긴 하는데, 그럴 때는 정말 불안해요. 주로 캠퍼스를 걸을 때 느껴지는데, 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이에요. 지나갈 때까지 주변 건물이랑 학생들이 조금 비현실적으로 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 스트레스를 받거나 불안할 때, 마치 자신의 몸 밖에서 스스로를 지켜보는 것 같거나 주변 세상이 진짜가 아닌 것처럼 느껴진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 스트레스받을 때 가장 많이 그런 것 같아요. 캠퍼스를 걷다가 갑자기 유리 너머로 모든 걸 보는 것 같아져요. 몸에 완전히 있는 느낌이 안 들고, 주변 건물이랑 학생들이 좀 비현실적으로 보여요. 그럴 때마다 정말 무서워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 이런 느낌이 들 때, 심장이 빨리 뛰거나 땀이 나거나 나쁜 일이 일어날 것 같은, 공황발작 같은 증상도 함께 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 땀이 나거나 심장이 심하게 빨리 뛰는 건 딱히 못 느낀 것 같아요. 그보다는 그럴 때 무섭고 불안한 느낌이 드는 건데, 그게 공황발작 같은 건지는 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 몸에 완전히 있지 않거나 주변이 비현실적으로 느껴질 때, 도망칠 수 없다는 느낌이나 갑자기 나쁜 일이 일어날 것 같은 두려움의 파도 같은 것도 함께 느끼시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 도망칠 수 없다는 느낌이라고까지는 말 못 할 것 같아요. 그보다는 모든 게 이상하고 비현실적으로 느껴져서 갑자기 무서운 느낌이 드는 거예요. 그럴 때 무섭긴 한데, 정확히 '나쁜 일이 일어날 것 같다'는 느낌인지는 잘 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 이런 비현실감과 동떨어진 느낌이 캠퍼스를 걷는 것 같은 특정 상황에서만 일어나나요, 아니면 특별히 불안하지 않을 때도 뚜렷한 이유 없이 갑자기 나타나나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 주로 특정 상황, 특히 캠퍼스를 걸을 때랑 연결되는 것 같아요. 그때가 가장 무서운데, 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이 들거든요. 주변 건물이랑 사람들이 좀 비현실적으로 보여요. 완전히 차분할 때 갑자기 나타난다고는 말 못 하겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사 질문] 본인 방이나 익숙한 장소처럼 그 특정 상황이 아닐 때도 이런 비현실감이나 동떨어진 느낌이 든 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 환자 응답] 방이나 익숙한 곳에서는 그렇게 많이 느껴지지 않아요. 정말 캠퍼스를 걸을 때가 더 심해요. 그때 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이 들어요... 주변 건물이랑 학생들이 완전히 진짜가 아닌 것 같고요. 그 부분이 저를 무섭게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>[10번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사 질문] 캠퍼스를 걷는 상황이 아니더라도, 잠깐이라도 자신과 동떨어진 느낌이나 세상이 비현실적으로 느껴지는 순간을 경험하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 환자 응답] 잠깐씩은 있을 수도 있는데, 진짜로 제가 느끼는 건 주로 캠퍼스를 걸을 때예요. 그때가 제일 심한데, 유리 너머로 모든 걸 보는 것 같고 몸에 제대로 있지 않은 느낌이에요. 건물이랑 다른 학생들이 좀 비현실적으로 보이고, 그게 저를 무섭게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>[11번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사 질문] 캠퍼스를 걷지 않을 때, 예를 들어 조용히 앉아 있거나 익숙한 장소에 있을 때도 이런 비현실감이나 동떨어진 느낌을 경험하신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 환자 응답] 조용히 앉아 있거나 익숙한 곳에서는 딱히 그렇지 않아요. 정말 무서운 부분은 캠퍼스를 걸을 때인데, 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이에요. 주변 건물이랑 학생들이 좀 비현실적으로 보여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>[12번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사 질문] 누군가와 대화하거나 일상적인 일을 할 때처럼 작은 순간에도 자신과 동떨어지거나 주변이 진짜가 아닌 것 같은 느낌을 받은 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 환자 응답] 평범한 대화나 일상적인 일 중에는 딱히, 적어도 제가 느낄 만큼은 아니에요. 주로 캠퍼스를 걸을 때예요. 그때 무서운데, 유리 너머로 모든 걸 보는 것 같고 제 몸에 완전히 있지 않은 느낌이 들어요. 주변 건물이랑 사람들이 살짝 비현실적으로 보여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>[13번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사 질문] TV를 보거나 숙제를 하거나 친구와 이야기하는 것 같은 일상적인 순간에도 조금이라도 자신과 동떨어지거나 주변이 살짝 비현실적으로 느껴진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 환자 응답] TV나 숙제 같은 걸 할 때는 딱히 아니에요. 그러니까, 가끔 딴생각을 할 수는 있는데, 그거랑 같은 느낌은 아니에요. 여전히 무서운 부분은 캠퍼스를 걸을 때인데, 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이에요. 건물이랑 학생들이 좀 비현실적으로 보여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>[14번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사 질문] 다른 곳을 걷거나 차를 타거나 그냥 사람들 속에 서 있는 것 같은 순간에도 조금이라도 자신과 동떨어지거나 주변이 살짝 비현실적으로 느껴진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 환자 응답] 주로 캠퍼스를 걸을 때예요. 차를 타거나 그냥 서 있을 때는 딱히 못 느껴요, 근데 캠퍼스에서는 유리 뒤에 있는 것처럼, 몸에 제대로 있지 않은 것처럼 느껴져요. 주변 건물이랑 학생들이 좀 비현실적으로 보이고, 그게 저를 무섭게 하는 부분이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>[15번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사 질문] 다른 곳을 걷거나 줄을 서 있거나 그냥 방을 둘러보는 것처럼 아주 가볍거나 짧은 순간에도 조금이나마 자신과 동떨어지거나 주변이 살짝 비현실적으로 느껴진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 환자 응답] 방에 있거나 줄 서 있을 때는 딱히 못 느껴요. 여전히 주로 캠퍼스를 걸을 때예요. 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이 들고, 주변 건물이랑 학생들이 좀 비현실적으로 보여요. 그게 제일 무서워요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>[16번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사 질문] 다른 곳을 걷거나 줄을 서 있거나 그냥 방을 둘러보는 것처럼 아주 가볍거나 짧은 순간에도 조금이나마 자신과 동떨어지거나 주변이 살짝 비현실적으로 느껴진 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 환자 응답] 여전히 대부분 그 캠퍼스 관련된 거예요. 그냥 방을 둘러볼 때는 딱히 그런 느낌이 안 드는데, 캠퍼스를 걸을 때는 유리 너머로 모든 걸 보는 것 같은 느낌이 들어요. 몸에 제대로 있지 않은 느낌이고, 주변 건물이랑 학생들이 좀 비현실적으로 보여요. 그 부분이 저를 무섭게 해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>[17번째 턴 · 의사의 감별진단] 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>진단명: 급성 스트레스장애 (D019)
 인구통계: 성별 여성 / 나이 42 / 직업상태 teaching assistant / 최종학력 대학원 졸업
@@ -573,425 +934,34 @@
 증상 지속 기간: 6 days
 추가 요건: 
 주호소 증상 코드: S082
-배경 서술: 에이다는 기존 담당자가 갑작스럽게 그만두면서 학생 예술·창업 쇼케이스를 인계받아 달라는 요청을 최근에 받았는데, 이는 평소 그녀가 맡던 조교 역할에서 크게 확장된 업무였다. 행사 도중 캠퍼스 아트리움에 설치된 임시 조명 장치가 붐비는 공간에서 무너져 내렸고, 에이다는 학생들을 뒤로 끌어당길 수 있을 만큼 가까이 있었지만, 한 자원봉사자가 그녀 눈앞에서 심각한 부상을 입었다. 그 후 6일 동안 그녀는 아트리움으로 돌아가지도, 쇼케이스에 대해 이야기하지도 못했고, 붕괴 당시의 기억이 계속 떠올랐으며, 캠퍼스에서 묘하게 붕 뜬 느낌을 받았고, 정원 가꾸기나 독서 모임, 남편이 위로해 주려는 노력도 즐기지 못했으며, 작은 소음이나 질문에도 놀라며 날카롭게 반응하기 시작했다. 그녀가 화를 내며 수업 계획 회의를 나가버리고 예정된 멘토링 세션을 두 차례 놓친 뒤, 대학의 근로자 지원 상담사가 긴급 정신과 평가를 주선했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 병원에 오신 것을 환영합니다. 오늘 어떤 일로 오셨는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 요즘 너무 이상하고 무서운 느낌이 들어서 왔어요. 캠퍼스를 걸어갈 때면 마치 유리 너머로 모든 걸 보는 것 같고, 제 몸 안에 완전히 있지 않은 것 같은 느낌이 들어요. 주변 건물이랑 학생들이 뭔가 진짜가 아닌 것처럼 느껴지는데, 그게 저를 무섭게 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 요즘 거의 매일, 하루 대부분 기분이 가라앉거나 우울하다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 그런 것 같지는 않아요. 그러니까, 속상하고 무섭긴 했는데, 매일 하루 대부분 우울했다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이런 비현실감이나 자신과 동떨어진 느낌이 자주 일어나나요, 아니면 왔다 갔다 하나요? 이런 느낌을 겪으신 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 왔다 갔다 하는데, 그래도 꽤 자주 일어나서 정말 무서워요. 주로 캠퍼스를 걸어갈 때 갑자기 유리 너머로 모든 걸 보고 있는 것 같은 느낌이 들어요, 제 몸에 완전히 있지 않은 것처럼요. 주변 건물이랑 사람들이 한동안 그냥 비현실적으로 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이런 비현실감과 동떨어진 느낌이 특정한 일로 스트레스를 받거나 불안할 때 더 자주 일어나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 네, 이미 긴장했거나 걱정될 때 더 그런 것 같아요. 근데 정말 저를 무섭게 하는 부분은 캠퍼스를 걸어갈 때 갑자기 유리 너머로 모든 걸 보는 느낌이 드는 거예요, 제 몸에 완전히 있지 않은 것처럼요. 주변 건물이랑 학생들이 그냥... 뭔가 진짜가 아닌 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이런 비현실감이나 자신과 동떨어진 느낌이 오래 지속되나요, 아니면 늘 시간이 지나면 사라지나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 시간이 지나면 사라지긴 하는데, 그럴 때는 정말 불안해요. 주로 캠퍼스를 걸을 때 느껴지는데, 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이에요. 지나갈 때까지 주변 건물이랑 학생들이 조금 비현실적으로 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 스트레스를 받거나 불안할 때, 마치 자신의 몸 밖에서 스스로를 지켜보는 것 같거나 주변 세상이 진짜가 아닌 것처럼 느껴진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 스트레스받을 때 가장 많이 그런 것 같아요. 캠퍼스를 걷다가 갑자기 유리 너머로 모든 걸 보는 것 같아져요. 몸에 완전히 있는 느낌이 안 들고, 주변 건물이랑 학생들이 좀 비현실적으로 보여요. 그럴 때마다 정말 무서워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 이런 느낌이 들 때, 심장이 빨리 뛰거나 땀이 나거나 나쁜 일이 일어날 것 같은, 공황발작 같은 증상도 함께 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 잘 모르겠어요. 땀이 나거나 심장이 심하게 빨리 뛰는 건 딱히 못 느낀 것 같아요. 그보다는 그럴 때 무섭고 불안한 느낌이 드는 건데, 그게 공황발작 같은 건지는 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 몸에 완전히 있지 않거나 주변이 비현실적으로 느껴질 때, 도망칠 수 없다는 느낌이나 갑자기 나쁜 일이 일어날 것 같은 두려움의 파도 같은 것도 함께 느끼시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 도망칠 수 없다는 느낌이라고까지는 말 못 할 것 같아요. 그보다는 모든 게 이상하고 비현실적으로 느껴져서 갑자기 무서운 느낌이 드는 거예요. 그럴 때 무섭긴 한데, 정확히 '나쁜 일이 일어날 것 같다'는 느낌인지는 잘 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 이런 비현실감과 동떨어진 느낌이 캠퍼스를 걷는 것 같은 특정 상황에서만 일어나나요, 아니면 특별히 불안하지 않을 때도 뚜렷한 이유 없이 갑자기 나타나나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 주로 특정 상황, 특히 캠퍼스를 걸을 때랑 연결되는 것 같아요. 그때가 가장 무서운데, 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이 들거든요. 주변 건물이랑 사람들이 좀 비현실적으로 보여요. 완전히 차분할 때 갑자기 나타난다고는 말 못 하겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사 질문] 본인 방이나 익숙한 장소처럼 그 특정 상황이 아닐 때도 이런 비현실감이나 동떨어진 느낌이 든 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 환자 응답] 방이나 익숙한 곳에서는 그렇게 많이 느껴지지 않아요. 정말 캠퍼스를 걸을 때가 더 심해요. 그때 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이 들어요... 주변 건물이랑 학생들이 완전히 진짜가 아닌 것 같고요. 그 부분이 저를 무섭게 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>[10번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사 질문] 캠퍼스를 걷는 상황이 아니더라도, 잠깐이라도 자신과 동떨어진 느낌이나 세상이 비현실적으로 느껴지는 순간을 경험하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 환자 응답] 잠깐씩은 있을 수도 있는데, 진짜로 제가 느끼는 건 주로 캠퍼스를 걸을 때예요. 그때가 제일 심한데, 유리 너머로 모든 걸 보는 것 같고 몸에 제대로 있지 않은 느낌이에요. 건물이랑 다른 학생들이 좀 비현실적으로 보이고, 그게 저를 무섭게 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>[11번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사 질문] 캠퍼스를 걷지 않을 때, 예를 들어 조용히 앉아 있거나 익숙한 장소에 있을 때도 이런 비현실감이나 동떨어진 느낌을 경험하신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 환자 응답] 조용히 앉아 있거나 익숙한 곳에서는 딱히 그렇지 않아요. 정말 무서운 부분은 캠퍼스를 걸을 때인데, 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이에요. 주변 건물이랑 학생들이 좀 비현실적으로 보여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>[12번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사 질문] 누군가와 대화하거나 일상적인 일을 할 때처럼 작은 순간에도 자신과 동떨어지거나 주변이 진짜가 아닌 것 같은 느낌을 받은 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 환자 응답] 평범한 대화나 일상적인 일 중에는 딱히, 적어도 제가 느낄 만큼은 아니에요. 주로 캠퍼스를 걸을 때예요. 그때 무서운데, 유리 너머로 모든 걸 보는 것 같고 제 몸에 완전히 있지 않은 느낌이 들어요. 주변 건물이랑 사람들이 살짝 비현실적으로 보여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>[13번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사 질문] TV를 보거나 숙제를 하거나 친구와 이야기하는 것 같은 일상적인 순간에도 조금이라도 자신과 동떨어지거나 주변이 살짝 비현실적으로 느껴진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 환자 응답] TV나 숙제 같은 걸 할 때는 딱히 아니에요. 그러니까, 가끔 딴생각을 할 수는 있는데, 그거랑 같은 느낌은 아니에요. 여전히 무서운 부분은 캠퍼스를 걸을 때인데, 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이에요. 건물이랑 학생들이 좀 비현실적으로 보여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>[14번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사 질문] 다른 곳을 걷거나 차를 타거나 그냥 사람들 속에 서 있는 것 같은 순간에도 조금이라도 자신과 동떨어지거나 주변이 살짝 비현실적으로 느껴진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 환자 응답] 주로 캠퍼스를 걸을 때예요. 차를 타거나 그냥 서 있을 때는 딱히 못 느껴요, 근데 캠퍼스에서는 유리 뒤에 있는 것처럼, 몸에 제대로 있지 않은 것처럼 느껴져요. 주변 건물이랑 학생들이 좀 비현실적으로 보이고, 그게 저를 무섭게 하는 부분이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>[15번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사 질문] 다른 곳을 걷거나 줄을 서 있거나 그냥 방을 둘러보는 것처럼 아주 가볍거나 짧은 순간에도 조금이나마 자신과 동떨어지거나 주변이 살짝 비현실적으로 느껴진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 환자 응답] 방에 있거나 줄 서 있을 때는 딱히 못 느껴요. 여전히 주로 캠퍼스를 걸을 때예요. 유리 너머로 모든 걸 보는 것 같고 몸에 완전히 있지 않은 느낌이 들고, 주변 건물이랑 학생들이 좀 비현실적으로 보여요. 그게 제일 무서워요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>[16번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 의사 질문] 다른 곳을 걷거나 줄을 서 있거나 그냥 방을 둘러보는 것처럼 아주 가볍거나 짧은 순간에도 조금이나마 자신과 동떨어지거나 주변이 살짝 비현실적으로 느껴진 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>[17번째 턴 · 환자 응답] 여전히 대부분 그 캠퍼스 관련된 거예요. 그냥 방을 둘러볼 때는 딱히 그런 느낌이 안 드는데, 캠퍼스를 걸을 때는 유리 너머로 모든 걸 보는 것 같은 느낌이 들어요. 몸에 제대로 있지 않은 느낌이고, 주변 건물이랑 학생들이 좀 비현실적으로 보여요. 그 부분이 저를 무섭게 해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
+배경 서술: 에이다는 기존 담당자가 갑작스럽게 그만두면서 학생 예술·창업 쇼케이스를 인계받아 달라는 요청을 최근에 받았는데, 이는 평소 그녀가 맡던 조교 역할에서 크게 확장된 업무였다. 행사 도중 캠퍼스 아트리움에 설치된 임시 조명 장치가 붐비는 공간에서 무너져 내렸고, 에이다는 학생들을 뒤로 끌어당길 수 있을 만큼 가까이 있었지만, 한 자원봉사자가 그녀 눈앞에서 심각한 부상을 입었다. 그 후 6일 동안 그녀는 아트리움으로 돌아가지도, 쇼케이스에 대해 이야기하지도 못했고, 붕괴 당시의 기억이 계속 떠올랐으며, 캠퍼스에서 묘하게 붕 뜬 느낌을 받았고, 정원 가꾸기나 독서 모임, 남편이 위로해 주려는 노력도 즐기지 못했으며, 작은 소음이나 질문에도 놀라며 날카롭게 반응하기 시작했다. 그녀가 화를 내며 수업 계획 회의를 나가버리고 예정된 멘토링 세션을 두 차례 놓친 뒤, 대학의 근로자 지원 상담사가 긴급 정신과 평가를 주선했다.
+표집된 증상 목록:
+  - S069 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - S070 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.
+  - S076 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - S077 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.
+  - S080 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.
+  - S082 이인증/비현실감: 외상 사건 이후 자기 자신이나 주변 환경에 대한 현실감이 변화된 상태.</t>
+        </is>
+      </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>[17번째 턴 · 의사의 감별진단] 중간확률: 범불안장애 (D011); 급성 스트레스장애 (D019) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: None (None, ICD: F44.4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: acute_stress_symptoms (관계=must_include, 요구개수=6, 충족개수=1, 커버리지=0.1667)
-  확인된 근거: 이인증/비현실감: 외상 사건 이후 자기 자신이나 주변 환경에 대한 현실감이 변화된 상태.
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.; 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.; 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).; 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).; 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.; 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.; 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.</t>
+          <t>의사의 최종 진단: None (None, ICD: F44.4)
+지속 기간 요건: 없음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: acute_stress_symptoms (관계=must_include, 요구개수=6, 충족개수=1, 커버리지=0.1667)
+확인된 근거:
+  - 이인증/비현실감: 외상 사건 이후 자기 자신이나 주변 환경에 대한 현실감이 변화된 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D019_S005_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S005_P001__qwen3-235b_kor.xlsx
@@ -920,6 +920,11 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -957,11 +962,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A67:B67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D019_S005_P001__qwen3-235b_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S005_P001__qwen3-235b_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
     </row>
     <row r="8">
@@ -553,6 +554,7 @@
         <v>0.25</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
